--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BE91F1-94CB-4F86-B5B5-013A52E87FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27584728-E51F-4990-964E-48627029242D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="144">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -297,13 +297,210 @@
   </si>
   <si>
     <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: </t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YURI FRANCISCO MELO DE OLIVEIRA GOMES        </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, de INCÊNDIO E ROUBO para COMPREENSIVA, ocorre a redução de 1 cla
+sse debônus, assim sendo o correto bônus 1.&lt;br&gt;Com a correção fico
+u 10x R$ 250,29. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMANDA MARTINS PEREIRA                       </t>
+  </si>
+  <si>
+    <t>Pedido do segurado, fez outra proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO DE ALMEIDA PRADO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILSON ALVES DE MELO                         </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA OLIVEIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROQUE DA SILVA                               </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ VALDEMIR DE FREITAS                     </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 10.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N L MOVEIS PLANEJADOS LTDA ME                </t>
+  </si>
+  <si>
+    <t>RECUSA FRUSTRADO * PRAZO EXPIRADO * CHASSI FOTO DO LOCAL INCORRETO E MOTOR FOTO EMBAÇADA</t>
+  </si>
+  <si>
+    <t>ALFA FOODS DISTRIBUIDORA DE ALIMENTOS LTDA EP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSUE DE OLIVEIRA EL                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARMISON MENDES DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANE PAULA DA SILVA ME                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FERNANDO DA SILVA CAVALHEIRO            </t>
+  </si>
+  <si>
+    <t>REPIQUE, FOTOS INCORRETAS: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALDO JORGE LOPES DA SILVA FILHO           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDETE ALVES AFONSO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA PESSOA GAMA CAVALCANTI                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO HENRIQUE HELENO                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Número do Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCADO SANT ANA LTDA ME                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO SANTOS LIMA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUGO LEONARDO DA ROCHA SILVA                 </t>
+  </si>
+  <si>
+    <t>Apólice a renovar já utilizada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AILTON PEREIRA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA DE ALMEIDA CARVALHO                  </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE LUIS ROUSSELET LAFRATTA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA DO SOCORRO SILVA                       </t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+Com a alteração no n° da CI o bônus passa à ser 0 em 10x R$ 314,65
+. Aguardamos o de acordo para emissão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANA CRISTINE DA SILVA RODRIGUES          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTAVIO ARTUR DE QUEIROZ JUNIOR               </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 2. &lt;br&gt;Com a correção fico
+u 10x R$ 456,52. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA APARECIDA NASCIMENTO BARBETA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBENS PARDINI                               </t>
+  </si>
+  <si>
+    <t>Correção de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAM ALEXANDRE FRANCISCO DOS SANTOS       </t>
+  </si>
+  <si>
+    <t>L GOMES COMERCIO VAREJISTA DE MERCADORIAS E F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEIR LOPES SEIXAS                           </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) ADEIR LOPES SEIXAS , pois este não consta como condutor na apó
+lice anterior. &lt;br&gt;&lt;br&gt;Neste caso estamos nesta data efetuando a
+recusa desta proposta. &lt;br&gt;&lt;br&gt;Orientamos transmitir um novo proce
+sso como SeguroNovo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECIO CARVALHO WEHBE                         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) DECIO CARVALHO WEHBE, pois este não consta como condutor na ap
+ólice anterior. &lt;br&gt;&lt;br&gt;Neste caso estamos nesta data efetuando a
+recusa desta proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEILA ALICE KOPPER                           </t>
+  </si>
+  <si>
+    <t>**FRUSTRADO** CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: HODÔMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMBO </t>
+  </si>
+  <si>
+    <t>FREITAS PANIFICADORA LTDA CNPJ 13782899000193</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t>MFB MODAS INDUSTRIA E COMERCIO LTDA ME CNPJ 49234405000183</t>
+  </si>
+  <si>
+    <t>Luiz Gustavo Piloto CPF/CNPJ 02111467812</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +543,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -361,7 +565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -547,12 +751,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -630,10 +858,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -696,12 +920,43 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1092,13 +1347,13 @@
       <c r="F2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="58"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1119,13 +1374,13 @@
       <c r="F3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="47"/>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -1146,13 +1401,13 @@
       <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="45">
         <v>45960</v>
       </c>
     </row>
@@ -1175,13 +1430,13 @@
       <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1204,13 +1459,13 @@
       <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1233,13 +1488,13 @@
       <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="G7" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1262,13 +1517,13 @@
       <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1291,13 +1546,13 @@
       <c r="F9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1320,13 +1575,13 @@
       <c r="F10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1349,13 +1604,13 @@
       <c r="F11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="49" t="s">
+      <c r="G11" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="45">
         <v>45964</v>
       </c>
     </row>
@@ -1378,13 +1633,13 @@
       <c r="F12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="49" t="s">
+      <c r="G12" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1407,13 +1662,13 @@
       <c r="F13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1436,13 +1691,13 @@
       <c r="F14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="45">
         <v>45965</v>
       </c>
     </row>
@@ -1465,13 +1720,13 @@
       <c r="F15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="49" t="s">
+      <c r="G15" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="45">
         <v>45965</v>
       </c>
     </row>
@@ -1494,13 +1749,13 @@
       <c r="F16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="49" t="s">
+      <c r="G16" s="47" t="s">
         <v>36</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="45">
         <v>45971</v>
       </c>
     </row>
@@ -1523,13 +1778,13 @@
       <c r="F17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="47" t="s">
         <v>39</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="45">
         <v>45968</v>
       </c>
     </row>
@@ -1552,13 +1807,13 @@
       <c r="F18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="49" t="s">
+      <c r="G18" s="47" t="s">
         <v>39</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="45">
         <v>45968</v>
       </c>
     </row>
@@ -1581,13 +1836,13 @@
       <c r="F19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="47">
+      <c r="I19" s="45">
         <v>45966</v>
       </c>
     </row>
@@ -1610,13 +1865,13 @@
       <c r="F20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="49" t="s">
+      <c r="G20" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="47">
+      <c r="I20" s="45">
         <v>45966</v>
       </c>
     </row>
@@ -1639,13 +1894,13 @@
       <c r="F21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="49" t="s">
+      <c r="G21" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="47">
+      <c r="I21" s="45">
         <v>45966</v>
       </c>
     </row>
@@ -1668,13 +1923,13 @@
       <c r="F22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="49" t="s">
+      <c r="G22" s="47" t="s">
         <v>48</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I22" s="47">
+      <c r="I22" s="45">
         <v>45966</v>
       </c>
     </row>
@@ -1697,13 +1952,13 @@
       <c r="F23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="49" t="s">
+      <c r="G23" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="45">
         <v>45967</v>
       </c>
     </row>
@@ -1726,13 +1981,13 @@
       <c r="F24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="49" t="s">
+      <c r="G24" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="47">
+      <c r="I24" s="45">
         <v>45966</v>
       </c>
     </row>
@@ -1755,13 +2010,13 @@
       <c r="F25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="47">
+      <c r="I25" s="45">
         <v>45960</v>
       </c>
     </row>
@@ -1784,13 +2039,13 @@
       <c r="F26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="49" t="s">
+      <c r="G26" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="47">
+      <c r="I26" s="45">
         <v>45959</v>
       </c>
     </row>
@@ -1813,13 +2068,13 @@
       <c r="F27" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="49" t="s">
+      <c r="G27" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1842,13 +2097,13 @@
       <c r="F28" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="49" t="s">
+      <c r="G28" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="47">
+      <c r="I28" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1871,13 +2126,13 @@
       <c r="F29" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="47">
+      <c r="I29" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1900,13 +2155,13 @@
       <c r="F30" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="49" t="s">
+      <c r="G30" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="47">
+      <c r="I30" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1929,13 +2184,13 @@
       <c r="F31" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="47">
+      <c r="I31" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1958,13 +2213,13 @@
       <c r="F32" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="G32" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="47">
+      <c r="I32" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -1987,13 +2242,13 @@
       <c r="F33" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="49" t="s">
+      <c r="G33" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2016,13 +2271,13 @@
       <c r="F34" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G34" s="49" t="s">
+      <c r="G34" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I34" s="47">
+      <c r="I34" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2045,13 +2300,13 @@
       <c r="F35" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="47">
+      <c r="I35" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2074,13 +2329,13 @@
       <c r="F36" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G36" s="49" t="s">
+      <c r="G36" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I36" s="47">
+      <c r="I36" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2103,13 +2358,13 @@
       <c r="F37" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="47">
+      <c r="I37" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2132,13 +2387,13 @@
       <c r="F38" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="49" t="s">
+      <c r="G38" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="47">
+      <c r="I38" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2161,13 +2416,13 @@
       <c r="F39" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="47">
+      <c r="I39" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2190,13 +2445,13 @@
       <c r="F40" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G40" s="49" t="s">
+      <c r="G40" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I40" s="47">
+      <c r="I40" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2219,13 +2474,13 @@
       <c r="F41" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I41" s="47">
+      <c r="I41" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2248,13 +2503,13 @@
       <c r="F42" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G42" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I42" s="47">
+      <c r="I42" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2277,13 +2532,13 @@
       <c r="F43" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G43" s="49" t="s">
+      <c r="G43" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I43" s="47">
+      <c r="I43" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2306,13 +2561,13 @@
       <c r="F44" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="49" t="s">
+      <c r="G44" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="47">
+      <c r="I44" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2335,13 +2590,13 @@
       <c r="F45" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="47">
+      <c r="I45" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2364,13 +2619,13 @@
       <c r="F46" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G46" s="49" t="s">
+      <c r="G46" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I46" s="47">
+      <c r="I46" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2393,13 +2648,13 @@
       <c r="F47" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G47" s="49" t="s">
+      <c r="G47" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="47">
+      <c r="I47" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2422,13 +2677,13 @@
       <c r="F48" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G48" s="49" t="s">
+      <c r="G48" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I48" s="47">
+      <c r="I48" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2451,13 +2706,13 @@
       <c r="F49" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G49" s="49" t="s">
+      <c r="G49" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I49" s="47">
+      <c r="I49" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2480,13 +2735,13 @@
       <c r="F50" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G50" s="49" t="s">
+      <c r="G50" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="47">
+      <c r="I50" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2509,13 +2764,13 @@
       <c r="F51" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G51" s="49" t="s">
+      <c r="G51" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I51" s="47">
+      <c r="I51" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2538,13 +2793,13 @@
       <c r="F52" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G52" s="49" t="s">
+      <c r="G52" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I52" s="47">
+      <c r="I52" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2567,13 +2822,13 @@
       <c r="F53" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G53" s="49" t="s">
+      <c r="G53" s="47" t="s">
         <v>17</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I53" s="47">
+      <c r="I53" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2596,13 +2851,13 @@
       <c r="F54" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="G54" s="56" t="s">
+      <c r="G54" s="54" t="s">
         <v>17</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I54" s="47">
+      <c r="I54" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2625,13 +2880,13 @@
       <c r="F55" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G55" s="56" t="s">
+      <c r="G55" s="54" t="s">
         <v>17</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I55" s="47">
+      <c r="I55" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2654,13 +2909,13 @@
       <c r="F56" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G56" s="49" t="s">
+      <c r="G56" s="47" t="s">
         <v>26</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="I56" s="47">
+      <c r="I56" s="45">
         <v>45961</v>
       </c>
     </row>
@@ -2671,9 +2926,9 @@
       <c r="D57" s="25"/>
       <c r="E57" s="18"/>
       <c r="F57" s="19"/>
-      <c r="G57" s="49"/>
+      <c r="G57" s="47"/>
       <c r="H57" s="13"/>
-      <c r="I57" s="47"/>
+      <c r="I57" s="45"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -2695,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2703,7 +2958,7 @@
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
@@ -2742,428 +2997,990 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D2" s="25">
+        <v>135139629</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450124469</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45941</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D3" s="25">
+        <v>135209860</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450131135</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="45">
+        <v>45972</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D4" s="25">
+        <v>135221704</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450132697</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="45">
+        <v>45964</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D5" s="25">
+        <v>135232441</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450133489</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="45">
+        <v>45965</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D6" s="25">
+        <v>135254726</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450135546</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="45">
+        <v>45966</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D7" s="25">
+        <v>135256118</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450135689</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="45">
+        <v>45966</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D8" s="25">
+        <v>135278219</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450137592</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D9" s="25">
+        <v>135281962</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450137845</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D10" s="25">
+        <v>135284036</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450138054</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D11" s="25">
+        <v>135273857</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450136998</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D12" s="25">
+        <v>135254177</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450135425</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="45">
+        <v>45966</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D13" s="25">
+        <v>135286512</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450138330</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D14" s="25">
+        <v>135296324</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450135656</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="45">
+        <v>45966</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D15" s="25">
+        <v>135244230</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450134743</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="45">
+        <v>45965</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D16" s="25">
+        <v>135256480</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450135700</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="45">
+        <v>45966</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="7">
+        <v>45990</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D17" s="25">
+        <v>135296616</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450138978</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D18" s="25">
+        <v>135220819</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450132631</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="45">
+        <v>45964</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D19" s="25">
+        <v>135219217</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450132455</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="45">
+        <v>45964</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D20" s="25">
+        <v>135251331</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450135106</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="64">
+        <v>45966</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D21" s="25">
+        <v>135161758</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450126735</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" s="64">
+        <v>45972</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45958</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D22" s="25">
+        <v>135131402</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450123480</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="64">
+        <v>45971</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45959</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D23" s="25">
+        <v>135156125</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450126064</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="64">
+        <v>45971</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D24" s="25">
+        <v>135253065</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450130981</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="65">
+        <v>45964</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45986</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D25" s="25">
+        <v>135162088</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450126779</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" s="64">
+        <v>45986</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D26" s="25">
+        <v>135275238</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450137218</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="64">
+        <v>45967</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45985</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D27" s="25">
+        <v>135201182</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450130410</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="I27" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45962</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D28" s="25">
+        <v>135205349</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450130838</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="45">
+        <v>45962</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D29" s="25">
+        <v>135228384</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450133038</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="45">
+        <v>45972</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D30" s="25">
+        <v>135239277</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450134138</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="45">
+        <v>45965</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D31" s="25">
+        <v>135240372</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450134325</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="45">
+        <v>45965</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="27"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C32" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D32" s="25">
+        <v>135265829</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450136558</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="I32" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="27"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C33" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D33" s="25">
+        <v>135266822</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450136613</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" s="45">
+        <v>45972</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="27"/>
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C34" s="28">
+        <v>45972</v>
+      </c>
+      <c r="D34" s="25">
+        <v>135281901</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3450137812</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="68"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="27"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="63"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="63"/>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9">
@@ -3173,8 +3990,8 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="63"/>
       <c r="I38"/>
     </row>
     <row r="39" spans="1:9">
@@ -3185,7 +4002,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
+      <c r="H39" s="15"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:9">
@@ -3331,50 +4148,20 @@
       <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:F34">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3422,7 +4209,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3430,37 +4217,79 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="61">
+        <v>46337</v>
+      </c>
+      <c r="C2" s="28">
+        <v>46002</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450143268</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="61">
+        <v>46337</v>
+      </c>
+      <c r="C3" s="28">
+        <v>46002</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450141915</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="61">
+        <v>45727</v>
+      </c>
+      <c r="C4" s="28">
+        <v>46002</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450131333</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -4616,7 +5445,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="38"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4649,8 +5478,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="27"/>
@@ -5180,7 +6009,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5196,8 +6025,8 @@
       <c r="D2" s="25"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="39"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="37"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
@@ -5209,8 +6038,8 @@
       <c r="D3" s="25"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="37"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
@@ -5222,8 +6051,8 @@
       <c r="D4" s="25"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
@@ -5235,8 +6064,8 @@
       <c r="D5" s="25"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="38"/>
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
@@ -5248,8 +6077,8 @@
       <c r="D6" s="25"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="39"/>
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
@@ -5261,8 +6090,8 @@
       <c r="D7" s="25"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="39"/>
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
@@ -5274,8 +6103,8 @@
       <c r="D8" s="25"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
@@ -5287,8 +6116,8 @@
       <c r="D9" s="25"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="39"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
@@ -5300,8 +6129,8 @@
       <c r="D10" s="25"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="39"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
@@ -5313,8 +6142,8 @@
       <c r="D11" s="25"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="39"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
@@ -5326,8 +6155,8 @@
       <c r="D12" s="25"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="39"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
@@ -5339,8 +6168,8 @@
       <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="39"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
@@ -5352,8 +6181,8 @@
       <c r="D14" s="25"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="39"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
@@ -5365,8 +6194,8 @@
       <c r="D15" s="25"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="39"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
@@ -5378,8 +6207,8 @@
       <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="39"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -5391,8 +6220,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="39"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
@@ -5404,8 +6233,8 @@
       <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="39"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
@@ -5413,9 +6242,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="23"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="34"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
     </row>
@@ -5426,7 +6255,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="34"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="9"/>
       <c r="I20" s="27"/>
     </row>
@@ -5437,7 +6266,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="34"/>
+      <c r="G21" s="32"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
     </row>
@@ -5448,7 +6277,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="34"/>
+      <c r="G22" s="32"/>
       <c r="H22" s="9"/>
       <c r="I22" s="27"/>
     </row>
@@ -5459,7 +6288,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="9"/>
       <c r="I23" s="27"/>
     </row>
@@ -5470,7 +6299,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="32"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -5881,22 +6710,22 @@
     <row r="2" spans="1:9">
       <c r="A2" s="6"/>
       <c r="B2" s="28"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="18"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="47"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="50"/>
+      <c r="C3" s="48"/>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="51"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="15"/>
       <c r="I3" s="11"/>
     </row>
@@ -5917,8 +6746,8 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="54"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="52"/>
       <c r="H5" s="13"/>
       <c r="I5" s="11"/>
     </row>
@@ -5929,7 +6758,7 @@
       <c r="D6" s="8"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="54"/>
+      <c r="G6" s="52"/>
       <c r="H6" s="12"/>
       <c r="I6" s="11"/>
     </row>
@@ -5940,7 +6769,7 @@
       <c r="D7" s="8"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="54"/>
+      <c r="G7" s="52"/>
       <c r="H7" s="12"/>
       <c r="I7" s="11"/>
     </row>

--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27584728-E51F-4990-964E-48627029242D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C89CBB6-77F8-409C-AEDF-9B35520C0CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="182">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: </t>
-  </si>
-  <si>
-    <t>28/10/2025</t>
   </si>
   <si>
     <t xml:space="preserve">YURI FRANCISCO MELO DE OLIVEIRA GOMES        </t>
@@ -494,6 +491,135 @@
   </si>
   <si>
     <t>Luiz Gustavo Piloto CPF/CNPJ 02111467812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON WAGNER MARGARIDO LOPES              </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026;&lt;br&gt; Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERAX SERVICOS E TELECOMUNICACAO LTDA EPP    </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE APARECIDA DA SILVA LINCH              </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) SIMONE APARECIDA DA SILVA LINCH, pois este não consta como con
+dutor na apólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIOGO KLOCK                                  </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEDITO CARDOSO                             </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU: Frente e lateral do passageiro, Frente e lateral do motorista, Traseira e lateral do passageiro, Painel com carro desligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANE FERNANDES DE SOUZA                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE LAT. DIR. E ESQ. CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE JOAO DE SOUZA                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CRLV, Frente e lateral do motorista, Traseira e lateral do motorista e do passageiro.</t>
+  </si>
+  <si>
+    <t>JULIANA APARECIDA PIANHO DE OLIVEIRA BARBIERI</t>
+  </si>
+  <si>
+    <t>REPIQUE, FOTOS INCORRETAS: CHASSI;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSENEIDE EVARISTO DA SILVA GALVAO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO FEZ O ENVIO DAS DEMAIS FOTOS Fotos que tiveram repique: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO LUIZ DA SILVA                        </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Painel com carro desligado // chassi ilegivel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGIA MARIA SILVA DE MORAES CARVALHO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIVIANE DA SILVA ANDRADE                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINA DE MORAES LENZI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELIO BERNARDES SILVA                        </t>
+  </si>
+  <si>
+    <t>Confirmação de bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILTON ALVES DE ARAUJO JUNIOR                </t>
+  </si>
+  <si>
+    <t>Pedido do cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILMAR ANTONIO SCALFONI                      </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 11.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 744 857 EMERSON Z                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS RODRIGUEZ                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNALVA N DE MARIA ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: TODAS AS FOTOS (FOTOS DE OUTO VEICULO) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUZELIA DIAS DE ALENCAR LUNA                 </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus. &lt;br&gt;Observação: A Liberação só poderá ser realizad
+a mediante documento solicitado, não serão aceitos protocolos
+ou qualquer outro documento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIANE DE PAULA BOLPETTI                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE LAT. DIR. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA SELMA BAIAO                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
   </si>
 </sst>
 </file>
@@ -780,7 +906,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -927,19 +1053,39 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2997,8 +3143,8 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>85</v>
+      <c r="B2" s="7">
+        <v>45958</v>
       </c>
       <c r="C2" s="28">
         <v>45972</v>
@@ -3010,13 +3156,13 @@
         <v>3450124469</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="57" t="s">
         <v>87</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>88</v>
       </c>
       <c r="I2" s="45">
         <v>45971</v>
@@ -3039,13 +3185,13 @@
         <v>3450131135</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>39</v>
       </c>
       <c r="H3" s="58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" s="45">
         <v>45972</v>
@@ -3068,7 +3214,7 @@
         <v>3450132697</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>26</v>
@@ -3097,13 +3243,13 @@
         <v>3450133489</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I5" s="45">
         <v>45965</v>
@@ -3126,7 +3272,7 @@
         <v>3450135546</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>17</v>
@@ -3155,13 +3301,13 @@
         <v>3450135689</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I7" s="45">
         <v>45966</v>
@@ -3184,13 +3330,13 @@
         <v>3450137592</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>39</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="45">
         <v>45971</v>
@@ -3213,13 +3359,13 @@
         <v>3450137845</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I9" s="45">
         <v>45967</v>
@@ -3242,7 +3388,7 @@
         <v>3450138054</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>17</v>
@@ -3271,7 +3417,7 @@
         <v>3450136998</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>17</v>
@@ -3300,7 +3446,7 @@
         <v>3450135425</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>17</v>
@@ -3329,7 +3475,7 @@
         <v>3450138330</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>17</v>
@@ -3358,13 +3504,13 @@
         <v>3450135656</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="45">
         <v>45966</v>
@@ -3387,13 +3533,13 @@
         <v>3450134743</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I15" s="45">
         <v>45965</v>
@@ -3416,13 +3562,13 @@
         <v>3450135700</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I16" s="45">
         <v>45966</v>
@@ -3445,13 +3591,13 @@
         <v>3450138978</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>39</v>
       </c>
       <c r="H17" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I17" s="45">
         <v>45971</v>
@@ -3474,13 +3620,13 @@
         <v>3450132631</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H18" s="58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I18" s="45">
         <v>45964</v>
@@ -3503,13 +3649,13 @@
         <v>3450132455</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I19" s="45">
         <v>45964</v>
@@ -3532,7 +3678,7 @@
         <v>3450135106</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>48</v>
@@ -3540,7 +3686,7 @@
       <c r="H20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I20" s="64">
+      <c r="I20" s="62">
         <v>45966</v>
       </c>
     </row>
@@ -3561,15 +3707,15 @@
         <v>3450126735</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I21" s="64">
+        <v>117</v>
+      </c>
+      <c r="I21" s="62">
         <v>45972</v>
       </c>
     </row>
@@ -3590,15 +3736,15 @@
         <v>3450123480</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>12</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="64">
+        <v>117</v>
+      </c>
+      <c r="I22" s="62">
         <v>45971</v>
       </c>
     </row>
@@ -3619,15 +3765,15 @@
         <v>3450126064</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="64">
+        <v>120</v>
+      </c>
+      <c r="I23" s="62">
         <v>45971</v>
       </c>
     </row>
@@ -3648,15 +3794,15 @@
         <v>3450130981</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>26</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="65">
+        <v>95</v>
+      </c>
+      <c r="I24" s="63">
         <v>45964</v>
       </c>
     </row>
@@ -3677,15 +3823,15 @@
         <v>3450126779</v>
       </c>
       <c r="F25" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="I25" s="64">
+      <c r="I25" s="62">
         <v>45986</v>
       </c>
     </row>
@@ -3706,7 +3852,7 @@
         <v>3450137218</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>26</v>
@@ -3714,7 +3860,7 @@
       <c r="H26" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="64">
+      <c r="I26" s="62">
         <v>45967</v>
       </c>
     </row>
@@ -3735,13 +3881,13 @@
         <v>3450130410</v>
       </c>
       <c r="F27" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="60" t="s">
         <v>126</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="67" t="s">
-        <v>127</v>
       </c>
       <c r="I27" s="45">
         <v>45967</v>
@@ -3764,7 +3910,7 @@
         <v>3450130838</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>17</v>
@@ -3793,13 +3939,13 @@
         <v>3450133038</v>
       </c>
       <c r="F29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="58" t="s">
         <v>129</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="58" t="s">
-        <v>130</v>
       </c>
       <c r="I29" s="45">
         <v>45972</v>
@@ -3822,7 +3968,7 @@
         <v>3450134138</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>17</v>
@@ -3851,7 +3997,7 @@
         <v>3450134325</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>17</v>
@@ -3880,13 +4026,13 @@
         <v>3450136558</v>
       </c>
       <c r="F32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="58" t="s">
         <v>133</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="62" t="s">
-        <v>134</v>
       </c>
       <c r="I32" s="45">
         <v>45971</v>
@@ -3909,13 +4055,13 @@
         <v>3450136613</v>
       </c>
       <c r="F33" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="58" t="s">
         <v>135</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33" s="62" t="s">
-        <v>136</v>
       </c>
       <c r="I33" s="45">
         <v>45972</v>
@@ -3938,13 +4084,13 @@
         <v>3450137812</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I34" s="45">
         <v>45967</v>
@@ -3958,8 +4104,8 @@
       <c r="E35" s="18"/>
       <c r="F35" s="13"/>
       <c r="G35" s="26"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="68"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="65"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -3969,7 +4115,7 @@
       <c r="E36" s="18"/>
       <c r="F36" s="13"/>
       <c r="G36" s="26"/>
-      <c r="H36" s="63"/>
+      <c r="H36" s="64"/>
       <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
@@ -3980,7 +4126,7 @@
       <c r="E37" s="23"/>
       <c r="F37" s="15"/>
       <c r="G37" s="52"/>
-      <c r="H37" s="63"/>
+      <c r="H37" s="64"/>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9">
@@ -3991,7 +4137,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
       <c r="G38" s="52"/>
-      <c r="H38" s="63"/>
+      <c r="H38" s="64"/>
       <c r="I38"/>
     </row>
     <row r="39" spans="1:9">
@@ -4171,7 +4317,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
@@ -4179,7 +4325,7 @@
     <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
     <col min="9" max="9" width="21" style="27" customWidth="1"/>
   </cols>
@@ -4218,344 +4364,741 @@
         <v>9</v>
       </c>
       <c r="B2" s="61">
-        <v>46337</v>
+        <v>45972</v>
       </c>
       <c r="C2" s="28">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" s="18">
         <v>3450143268</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>141</v>
-      </c>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="61">
-        <v>46337</v>
+        <v>45972</v>
       </c>
       <c r="C3" s="28">
-        <v>46002</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="18">
+        <v>45973</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="70">
         <v>3450141915</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>141</v>
-      </c>
+      <c r="H3" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="61">
-        <v>45727</v>
+        <v>45964</v>
       </c>
       <c r="C4" s="28">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E4" s="18">
         <v>3450131333</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>141</v>
-      </c>
+      <c r="H4" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="61">
+        <v>45960</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D5" s="74">
+        <v>135177676</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450128077</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="76" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="61">
+        <v>45967</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D6" s="74">
+        <v>135287008</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450138362</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I6" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="61">
+        <v>45996</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D7" s="74">
+        <v>135269259</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450136679</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D8" s="74">
+        <v>135309156</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450140111</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="61">
+        <v>45967</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D9" s="74">
+        <v>135298416</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450138043</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D10" s="74">
+        <v>135290497</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450138483</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D11" s="74">
+        <v>135296743</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450138990</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D12" s="74">
+        <v>135309865</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450140199</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D13" s="74">
+        <v>135292781</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450138648</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="61">
+        <v>45968</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D14" s="74">
+        <v>135291803</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450138604</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="61">
+        <v>45971</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D15" s="74">
+        <v>135318579</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450140540</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="B16" s="61">
+        <v>45972</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D16" s="74">
+        <v>135347242</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450142861</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="45">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="61">
+        <v>45960</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D17" s="74">
+        <v>135171871</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450127472</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="45">
+        <v>45973</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="61">
+        <v>45960</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D18" s="74">
+        <v>135178864</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450128242</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="45">
+        <v>45973</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D19" s="74">
+        <v>135191337</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450129144</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I19" s="45">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D20" s="74">
+        <v>135284850</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450138109</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="45">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D21" s="74">
+        <v>135340447</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450142091</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="45">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D22" s="74">
+        <v>135214192</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450131872</v>
+      </c>
+      <c r="F22" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="56">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D23" s="74">
+        <v>135222346</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450132851</v>
+      </c>
+      <c r="F23" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="I23" s="45">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D24" s="74">
+        <v>135200738</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450130387</v>
+      </c>
+      <c r="F24" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="45">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D25" s="74">
+        <v>135279407</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450137658</v>
+      </c>
+      <c r="F25" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="45">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45973</v>
+      </c>
+      <c r="D26" s="74">
+        <v>135265102</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450136460</v>
+      </c>
+      <c r="F26" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I26" s="45">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="D27" s="72"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
+      <c r="G28" s="24"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="28"/>
@@ -4565,7 +5108,7 @@
       <c r="G29" s="24"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="28"/>
@@ -4575,7 +5118,7 @@
       <c r="G30" s="24"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="28"/>
@@ -4585,7 +5128,7 @@
       <c r="G31" s="24"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="28"/>
@@ -4617,31 +5160,31 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="24"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="24"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
@@ -4685,43 +5228,23 @@
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A26" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B18" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A27:A34" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G34" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B20" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7283,6 +7806,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517947</_dlc_DocId>
@@ -7325,66 +7857,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41fed91b93125e9eb81167fcc17a074a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b37f844e38ab5d6be06af21bb96d53eb" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7762,18 +8235,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A257C1-04FF-4E6C-ACE9-5798DD40C91A}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B8E4FE8-D6E5-4E6B-A7A7-8E5BC5123295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C89CBB6-77F8-409C-AEDF-9B35520C0CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31F9883C-6293-4D9D-93F2-079F12BC37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="211">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -620,6 +620,116 @@
   </si>
   <si>
     <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t>WILLIAM DO PRADO CPF- 08668987860</t>
+  </si>
+  <si>
+    <t>DANA AGRO LTDA ME  CPF- 35262797000180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WANDERSON VICTOR RODRIGUES DE LIMA           </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado&lt;br&gt;&lt;b
+r&gt;Constatamos que o modelo do veículo informado na cotação difere
+do constado, segue abaixo informação retornada pelo sistema atravé
+s do chassi do veículo: &lt;br&gt;&lt;br&gt;Modelo constatado: HONDA HR-V EXL
+1.5 16V CVT FLEX AUT 4 PTS&lt;br&gt; &lt;br&gt;FIPE: 014110-0 R$ 170.650,00&lt;br
+&gt; &lt;br&gt;Valor do prêmio: 10x R$ 1.510,35&lt;br&gt;&lt;br&gt;Franquia: R$ 8.467,
+84&lt;br&gt;&lt;br&gt;Podemos emitir desse forma?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMETRIUS PEREIRA MARTINS DA SILVA           </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO BITTENCOURT DE OLIVEIRA                </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 através desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA CRISTINA DE ALMEIDA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido do segurado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAELA OLIVEIRA DE SANTANA GOMES            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) RAFAELA OLIVEIRA DE SANTANA GOMES, pois este não consta como c
+ondutor na apólice anterior. &lt;br&gt;Neste caso estamos nesta data ef
+etuando a recusa desta proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYGIA CABRAL OLIVEIRA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) LYGIA CABRAL OLIVEIRA, pois este não consta como condutor na a
+pólice anterior. &lt;br&gt;Neste caso estamos nesta data efetuando a re
+cusa desta proposta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISLANE APARECIDA SANTOS GUILHERME          </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 12/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO DE ARAUJO VIANNA SOARES             </t>
+  </si>
+  <si>
+    <t>Pedido do corretor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANA APARECIDA LAUERMANN BATISTA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELI DO PRADO PEREIRA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE LUIZ DE MORAES ADAO                    </t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+No aguardo do envio do endosso de cancelamento para prosseguirmos
+com a emissão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCADO AVENIDA LTDA ME                      </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Painel com carro desligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILDA MARIA DOS SANTOS                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026;&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA ANTUNES NASCIMENTO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA VITORIA DINIZ NARZETTI              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIRA MULLER RODRIGUES                       </t>
   </si>
 </sst>
 </file>
@@ -906,7 +1016,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1067,7 +1177,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1081,11 +1190,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4396,13 +4502,13 @@
       <c r="C3" s="28">
         <v>45973</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="70">
+      <c r="E3" s="69">
         <v>3450141915</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="70" t="s">
         <v>141</v>
       </c>
       <c r="G3" s="26" t="s">
@@ -4450,19 +4556,19 @@
       <c r="C5" s="28">
         <v>45973</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="25">
         <v>135177676</v>
       </c>
       <c r="E5" s="18">
         <v>3450128077</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="12" t="s">
         <v>143</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="76" t="s">
+      <c r="H5" s="13" t="s">
         <v>144</v>
       </c>
       <c r="I5" s="45">
@@ -4479,13 +4585,13 @@
       <c r="C6" s="28">
         <v>45973</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="25">
         <v>135287008</v>
       </c>
       <c r="E6" s="18">
         <v>3450138362</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="12" t="s">
         <v>145</v>
       </c>
       <c r="G6" s="26" t="s">
@@ -4508,19 +4614,19 @@
       <c r="C7" s="28">
         <v>45973</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="25">
         <v>135269259</v>
       </c>
       <c r="E7" s="18">
         <v>3450136679</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="12" t="s">
         <v>147</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="76" t="s">
+      <c r="H7" s="13" t="s">
         <v>148</v>
       </c>
       <c r="I7" s="45">
@@ -4537,13 +4643,13 @@
       <c r="C8" s="28">
         <v>45973</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="25">
         <v>135309156</v>
       </c>
       <c r="E8" s="18">
         <v>3450140111</v>
       </c>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="12" t="s">
         <v>149</v>
       </c>
       <c r="G8" s="26" t="s">
@@ -4566,13 +4672,13 @@
       <c r="C9" s="28">
         <v>45973</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="25">
         <v>135298416</v>
       </c>
       <c r="E9" s="18">
         <v>3450138043</v>
       </c>
-      <c r="F9" s="68" t="s">
+      <c r="F9" s="12" t="s">
         <v>151</v>
       </c>
       <c r="G9" s="26" t="s">
@@ -4595,13 +4701,13 @@
       <c r="C10" s="28">
         <v>45973</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="25">
         <v>135290497</v>
       </c>
       <c r="E10" s="18">
         <v>3450138483</v>
       </c>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="12" t="s">
         <v>153</v>
       </c>
       <c r="G10" s="67" t="s">
@@ -4624,13 +4730,13 @@
       <c r="C11" s="28">
         <v>45973</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="25">
         <v>135296743</v>
       </c>
       <c r="E11" s="18">
         <v>3450138990</v>
       </c>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="12" t="s">
         <v>155</v>
       </c>
       <c r="G11" s="26" t="s">
@@ -4653,13 +4759,13 @@
       <c r="C12" s="28">
         <v>45973</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="25">
         <v>135309865</v>
       </c>
       <c r="E12" s="18">
         <v>3450140199</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="12" t="s">
         <v>157</v>
       </c>
       <c r="G12" s="67" t="s">
@@ -4682,13 +4788,13 @@
       <c r="C13" s="28">
         <v>45973</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="25">
         <v>135292781</v>
       </c>
       <c r="E13" s="18">
         <v>3450138648</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="F13" s="12" t="s">
         <v>159</v>
       </c>
       <c r="G13" s="26" t="s">
@@ -4711,13 +4817,13 @@
       <c r="C14" s="28">
         <v>45973</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="25">
         <v>135291803</v>
       </c>
       <c r="E14" s="18">
         <v>3450138604</v>
       </c>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="12" t="s">
         <v>161</v>
       </c>
       <c r="G14" s="26" t="s">
@@ -4740,13 +4846,13 @@
       <c r="C15" s="28">
         <v>45973</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="25">
         <v>135318579</v>
       </c>
       <c r="E15" s="18">
         <v>3450140540</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="12" t="s">
         <v>163</v>
       </c>
       <c r="G15" s="26" t="s">
@@ -4769,13 +4875,13 @@
       <c r="C16" s="28">
         <v>45973</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="25">
         <v>135347242</v>
       </c>
       <c r="E16" s="18">
         <v>3450142861</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="F16" s="12" t="s">
         <v>164</v>
       </c>
       <c r="G16" s="26" t="s">
@@ -4798,13 +4904,13 @@
       <c r="C17" s="28">
         <v>45973</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="25">
         <v>135171871</v>
       </c>
       <c r="E17" s="18">
         <v>3450127472</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="12" t="s">
         <v>165</v>
       </c>
       <c r="G17" s="26" t="s">
@@ -4827,13 +4933,13 @@
       <c r="C18" s="28">
         <v>45973</v>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="25">
         <v>135178864</v>
       </c>
       <c r="E18" s="18">
         <v>3450128242</v>
       </c>
-      <c r="F18" s="68" t="s">
+      <c r="F18" s="12" t="s">
         <v>166</v>
       </c>
       <c r="G18" s="67" t="s">
@@ -4856,13 +4962,13 @@
       <c r="C19" s="28">
         <v>45973</v>
       </c>
-      <c r="D19" s="74">
+      <c r="D19" s="25">
         <v>135191337</v>
       </c>
       <c r="E19" s="18">
         <v>3450129144</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="F19" s="12" t="s">
         <v>168</v>
       </c>
       <c r="G19" s="26" t="s">
@@ -4885,13 +4991,13 @@
       <c r="C20" s="28">
         <v>45973</v>
       </c>
-      <c r="D20" s="74">
+      <c r="D20" s="25">
         <v>135284850</v>
       </c>
       <c r="E20" s="18">
         <v>3450138109</v>
       </c>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="12" t="s">
         <v>170</v>
       </c>
       <c r="G20" s="26" t="s">
@@ -4914,13 +5020,13 @@
       <c r="C21" s="28">
         <v>45973</v>
       </c>
-      <c r="D21" s="74">
+      <c r="D21" s="25">
         <v>135340447</v>
       </c>
       <c r="E21" s="18">
         <v>3450142091</v>
       </c>
-      <c r="F21" s="68" t="s">
+      <c r="F21" s="12" t="s">
         <v>172</v>
       </c>
       <c r="G21" s="26" t="s">
@@ -4943,19 +5049,19 @@
       <c r="C22" s="28">
         <v>45973</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D22" s="25">
         <v>135214192</v>
       </c>
       <c r="E22" s="18">
         <v>3450131872</v>
       </c>
-      <c r="F22" s="68" t="s">
+      <c r="F22" s="12" t="s">
         <v>173</v>
       </c>
       <c r="G22" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="75" t="s">
+      <c r="H22" s="73" t="s">
         <v>45</v>
       </c>
       <c r="I22" s="56">
@@ -4972,13 +5078,13 @@
       <c r="C23" s="28">
         <v>45973</v>
       </c>
-      <c r="D23" s="74">
+      <c r="D23" s="25">
         <v>135222346</v>
       </c>
       <c r="E23" s="18">
         <v>3450132851</v>
       </c>
-      <c r="F23" s="68" t="s">
+      <c r="F23" s="12" t="s">
         <v>174</v>
       </c>
       <c r="G23" s="26" t="s">
@@ -5001,19 +5107,19 @@
       <c r="C24" s="28">
         <v>45973</v>
       </c>
-      <c r="D24" s="74">
+      <c r="D24" s="25">
         <v>135200738</v>
       </c>
       <c r="E24" s="18">
         <v>3450130387</v>
       </c>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="12" t="s">
         <v>176</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="13" t="s">
         <v>177</v>
       </c>
       <c r="I24" s="45">
@@ -5030,13 +5136,13 @@
       <c r="C25" s="28">
         <v>45973</v>
       </c>
-      <c r="D25" s="74">
+      <c r="D25" s="25">
         <v>135279407</v>
       </c>
       <c r="E25" s="18">
         <v>3450137658</v>
       </c>
-      <c r="F25" s="68" t="s">
+      <c r="F25" s="12" t="s">
         <v>178</v>
       </c>
       <c r="G25" s="26" t="s">
@@ -5059,13 +5165,13 @@
       <c r="C26" s="28">
         <v>45973</v>
       </c>
-      <c r="D26" s="74">
+      <c r="D26" s="25">
         <v>135265102</v>
       </c>
       <c r="E26" s="18">
         <v>3450136460</v>
       </c>
-      <c r="F26" s="68" t="s">
+      <c r="F26" s="12" t="s">
         <v>180</v>
       </c>
       <c r="G26" s="26" t="s">
@@ -5082,8 +5188,8 @@
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="28"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="73"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="72"/>
       <c r="F27" s="34"/>
       <c r="G27" s="24"/>
       <c r="H27" s="15"/>
@@ -5252,7 +5358,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -5299,238 +5405,529 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45974</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450144830</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45973</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45974</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450143994</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="45"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D4" s="25">
+        <v>135202255</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450130607</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D5" s="25">
+        <v>135195250</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450129661</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D6" s="25">
+        <v>135216762</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450132213</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D7" s="25">
+        <v>135252707</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450135271</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="I7" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45989</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D8" s="25">
+        <v>135294771</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450138769</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="I8" s="45">
+        <v>45974</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45986</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D9" s="25">
+        <v>135293513</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450138703</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="I9" s="45">
+        <v>45974</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D10" s="25">
+        <v>135316201</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450140353</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="I10" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D11" s="25">
+        <v>135342549</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450133456</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="I11" s="45">
+        <v>45975</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D12" s="25">
+        <v>135337305</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450141134</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="45">
+        <v>45971</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45979</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D13" s="25">
+        <v>135342217</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450142366</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D14" s="25">
+        <v>135202087</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450130574</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="I14" s="45">
+        <v>45967</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D15" s="25">
+        <v>135296927</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450139044</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="I15" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D16" s="25">
+        <v>135191265</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450129122</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="I16" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D17" s="25">
+        <v>135296887</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450139011</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="45">
+        <v>45968</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D18" s="25">
+        <v>135254648</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450135513</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="I18" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45974</v>
+      </c>
+      <c r="D19" s="25">
+        <v>135241970</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450134468</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="45">
+        <v>45973</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5872,27 +6269,17 @@
       <c r="G54" s="6"/>
       <c r="H54" s="9"/>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 10.11.2025 a 16.11.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31F9883C-6293-4D9D-93F2-079F12BC37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA1E5427-22A2-497C-8B37-B78961E732BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10.11" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="272">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -730,6 +730,238 @@
   </si>
   <si>
     <t xml:space="preserve">MAIRA MULLER RODRIGUES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ALMEIDA NICODEMOS                      </t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+A informação da central de bônus (realizada nova confirmação hoje)
+, é que a apólice foi cancelada em 29/04/25, mas que ocorreu a ren
+ovação da mesma.&lt;br&gt;Precisamos da cópia dessa renovação e do endos
+so de cancelamento para análise e devidos ajustes do bônus para qu
+e não ocorra a emissão incorreta da apólice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIBIANA SALES ANTUNES BRUM                   </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve sinistro na apólice anterior, portanto a renovaçã
+o correta é externa com sinistro, conforme regra diminui uma class
+e de bônus, assim sendo o correto bônus 0. &lt;br&gt;Com a correção fico
+u 10x R$ 385,14. Podemos emitir desta forma?&lt;br&gt;&lt;br&gt;&lt;br&gt;&lt;br&gt;&lt;br&gt;PE
+NDÊNCIA 1735  ACEITAÇÃO CONDICIONADA Á CONFIRMAÇÃO NA CBE&lt;br&gt;&lt;br&gt;
+Conforme consulta nacentral de bônus, a apólice foi renovada na co
+ngênere de origem. Portanto, peço a gentileza de encaminhar a docu
+mentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere com
+vigência de 2025 a 2026; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOVANI AUGUSTO DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMUNDO LEITE DE SOUSA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANIO LIBARINO DA ROCHA ME                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPERIO ALICE PIZZARIA LTDA ME               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORETE CAMPI COMERCIAL LTDA EPP              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIO IAQUIS DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 13.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMANUELA PEREIRA DOS SANTOS OLIVEIRA         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) EMANUELA PEREIRA DOS SANTOS OLIVEIRA, pois este não consta com
+o condutor na apólice anterior. &lt;br&gt;Neste caso estamos nesta data
+efetuando a recusa desta proposta. Orientamos transmitir um novo
+processo como Seguro Novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACRIZIO DINIZ JUNQUEIRA FILHO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETICIA DEL ROIO VASCONCELLOS MIGITA         </t>
+  </si>
+  <si>
+    <t>Apólice ainda consta ativa, no aguardo do endosso de cancelamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL SOARES SANTOS                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) GABRIEL SOARES SANTOS, pois este não consta como condutor na a
+pólice anterior. &lt;br&gt;Neste caso estamos nesta data efetuando a re
+cusa desta proposta. Orientamos transmitir um novo processo como S
+eguro Novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERMISON BISPO DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C APARECIDA DERKOSKI LTDA ME                 </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA LUISA SANTIAGO DA SILVEIRA FONSECA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADIMILSON RAMOS OLIVEIRA                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senhor
+(a) ADIMILSON RAMOS OLIVEIRA, pois este não consta como condutor n
+a apólice anterior. &lt;br&gt;Neste caso estamos nesta data efetuando a
+recusa desta proposta. Orientamos transmitir um novo processo com
+o Seguro Novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA CRISTINA SARTORI JORGE                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAIENE CRISTINA MANOEL                       </t>
+  </si>
+  <si>
+    <t>RECUSA: FRUSTRADO PRAZO EXPIRADO * SEGURADO NÃO CORRIGIU OS PASSOS SOLICITADOS Fotos que tiveram repique: Traseira, Número do Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA MARIA DA SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA BONADIO SANTOS RIBEIRO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TINTAS ANGEL TEXTURAS E VERNIZES LTDA ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELY LEANDRO DA SILVA 426 477 542 68 ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARYSSA CRISTINA FABIANO DA SILVA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veículo informado é diferente do calculado.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHELLE FERNANDES GUIMARAES DA MATA         </t>
+  </si>
+  <si>
+    <t>Informamos que a p
+roposta em questão se encontra em duplicidade com a proposta 13500
+6804, para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAGNER MORAES GONCALVES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO TENORIO DA VITORIA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALDO DE ABREU ALVES                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2025 a 2026.&lt;br&gt; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO WANDERSON REIS DOS SANTOS 05821390311 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON DE OLIVEIRA CARDOSO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA SILVA MELO MARTINS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODILSON LA ROQUE SCHIMITEZ                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIMERIA CRISTINA DE SOUZA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELLINGTON RODRIGO SOARES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELI GUIMARAES DA COSTA SEVERO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELTON SOUSA CORREA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULISSES JOSE DOS SANTOS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATARINA LUCIA GOMES DE FARIA DIAS           </t>
+  </si>
+  <si>
+    <t>Informamos que a p
+roposta em questão se encontra em duplicidade com a proposta 13517
+1883, para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA CAROLINE SILVA DE MORAES               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA REGINA SCARPARO                     </t>
+  </si>
+  <si>
+    <t>identificado que o chassi informado não condiz com placa do veícul
+o, necessário o envio do CRLV para análise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELCIO DAL MOLIN                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORT PNEUS LTDA ME                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATANI TAVARES DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSIDAN SANTOS CARDOSO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL PIMENTEL BARBOZA                     </t>
+  </si>
+  <si>
+    <t>Informamos que a p
+roposta em questão se encontra em duplicidade com a proposta 13499
+7397, para prosseguirmos com a emissão se faz necessário realizar
+o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON DONIZETI ALVES                         </t>
   </si>
 </sst>
 </file>
@@ -801,7 +1033,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1011,6 +1243,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1097,34 +1349,10 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1191,13 +1419,49 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1599,13 +1863,13 @@
       <c r="F2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="56"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1626,13 +1890,13 @@
       <c r="F3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="37" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="45"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -1653,13 +1917,13 @@
       <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="35">
         <v>45960</v>
       </c>
     </row>
@@ -1682,13 +1946,13 @@
       <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1711,13 +1975,13 @@
       <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1740,13 +2004,13 @@
       <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1769,13 +2033,13 @@
       <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1798,13 +2062,13 @@
       <c r="F9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1827,13 +2091,13 @@
       <c r="F10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1856,13 +2120,13 @@
       <c r="F11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="35">
         <v>45964</v>
       </c>
     </row>
@@ -1885,13 +2149,13 @@
       <c r="F12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1914,13 +2178,13 @@
       <c r="F13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -1943,13 +2207,13 @@
       <c r="F14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -1972,13 +2236,13 @@
       <c r="F15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -2001,13 +2265,13 @@
       <c r="F16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="37" t="s">
         <v>36</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -2030,13 +2294,13 @@
       <c r="F17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="37" t="s">
         <v>39</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -2059,13 +2323,13 @@
       <c r="F18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="47" t="s">
+      <c r="G18" s="37" t="s">
         <v>39</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -2088,13 +2352,13 @@
       <c r="F19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G19" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -2117,13 +2381,13 @@
       <c r="F20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -2146,13 +2410,13 @@
       <c r="F21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -2175,13 +2439,13 @@
       <c r="F22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="37" t="s">
         <v>48</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I22" s="45">
+      <c r="I22" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -2204,13 +2468,13 @@
       <c r="F23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G23" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -2233,13 +2497,13 @@
       <c r="F24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -2262,13 +2526,13 @@
       <c r="F25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="G25" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="35">
         <v>45960</v>
       </c>
     </row>
@@ -2291,13 +2555,13 @@
       <c r="F26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="47" t="s">
+      <c r="G26" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="35">
         <v>45959</v>
       </c>
     </row>
@@ -2320,13 +2584,13 @@
       <c r="F27" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="47" t="s">
+      <c r="G27" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2349,13 +2613,13 @@
       <c r="F28" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="47" t="s">
+      <c r="G28" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="45">
+      <c r="I28" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2378,13 +2642,13 @@
       <c r="F29" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="47" t="s">
+      <c r="G29" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="45">
+      <c r="I29" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2407,13 +2671,13 @@
       <c r="F30" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="47" t="s">
+      <c r="G30" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="45">
+      <c r="I30" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2436,13 +2700,13 @@
       <c r="F31" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="47" t="s">
+      <c r="G31" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="45">
+      <c r="I31" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2465,13 +2729,13 @@
       <c r="F32" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="47" t="s">
+      <c r="G32" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="45">
+      <c r="I32" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2494,13 +2758,13 @@
       <c r="F33" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G33" s="47" t="s">
+      <c r="G33" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="45">
+      <c r="I33" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2523,13 +2787,13 @@
       <c r="F34" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G34" s="47" t="s">
+      <c r="G34" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H34" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2552,13 +2816,13 @@
       <c r="F35" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="47" t="s">
+      <c r="G35" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="45">
+      <c r="I35" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2581,13 +2845,13 @@
       <c r="F36" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G36" s="47" t="s">
+      <c r="G36" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I36" s="45">
+      <c r="I36" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2610,13 +2874,13 @@
       <c r="F37" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="47" t="s">
+      <c r="G37" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="45">
+      <c r="I37" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2639,13 +2903,13 @@
       <c r="F38" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="47" t="s">
+      <c r="G38" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="45">
+      <c r="I38" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2668,13 +2932,13 @@
       <c r="F39" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G39" s="47" t="s">
+      <c r="G39" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="45">
+      <c r="I39" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2697,13 +2961,13 @@
       <c r="F40" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G40" s="47" t="s">
+      <c r="G40" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I40" s="45">
+      <c r="I40" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2726,13 +2990,13 @@
       <c r="F41" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="47" t="s">
+      <c r="G41" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I41" s="45">
+      <c r="I41" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2755,13 +3019,13 @@
       <c r="F42" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="47" t="s">
+      <c r="G42" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I42" s="45">
+      <c r="I42" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2784,13 +3048,13 @@
       <c r="F43" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G43" s="47" t="s">
+      <c r="G43" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I43" s="45">
+      <c r="I43" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2813,13 +3077,13 @@
       <c r="F44" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="47" t="s">
+      <c r="G44" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="45">
+      <c r="I44" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2842,13 +3106,13 @@
       <c r="F45" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G45" s="47" t="s">
+      <c r="G45" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H45" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I45" s="45">
+      <c r="I45" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2871,13 +3135,13 @@
       <c r="F46" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G46" s="47" t="s">
+      <c r="G46" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I46" s="45">
+      <c r="I46" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2900,13 +3164,13 @@
       <c r="F47" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G47" s="47" t="s">
+      <c r="G47" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="45">
+      <c r="I47" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2929,13 +3193,13 @@
       <c r="F48" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G48" s="47" t="s">
+      <c r="G48" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I48" s="45">
+      <c r="I48" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2958,13 +3222,13 @@
       <c r="F49" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G49" s="47" t="s">
+      <c r="G49" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I49" s="45">
+      <c r="I49" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -2987,13 +3251,13 @@
       <c r="F50" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G50" s="47" t="s">
+      <c r="G50" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="45">
+      <c r="I50" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3016,13 +3280,13 @@
       <c r="F51" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G51" s="47" t="s">
+      <c r="G51" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I51" s="45">
+      <c r="I51" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3045,13 +3309,13 @@
       <c r="F52" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G52" s="47" t="s">
+      <c r="G52" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I52" s="45">
+      <c r="I52" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3074,13 +3338,13 @@
       <c r="F53" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I53" s="45">
+      <c r="I53" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3103,13 +3367,13 @@
       <c r="F54" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="G54" s="54" t="s">
+      <c r="G54" s="44" t="s">
         <v>17</v>
       </c>
       <c r="H54" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I54" s="45">
+      <c r="I54" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3132,13 +3396,13 @@
       <c r="F55" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G55" s="54" t="s">
+      <c r="G55" s="44" t="s">
         <v>17</v>
       </c>
       <c r="H55" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I55" s="45">
+      <c r="I55" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3161,13 +3425,13 @@
       <c r="F56" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G56" s="47" t="s">
+      <c r="G56" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="I56" s="45">
+      <c r="I56" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -3178,9 +3442,9 @@
       <c r="D57" s="25"/>
       <c r="E57" s="18"/>
       <c r="F57" s="19"/>
-      <c r="G57" s="47"/>
+      <c r="G57" s="37"/>
       <c r="H57" s="13"/>
-      <c r="I57" s="45"/>
+      <c r="I57" s="35"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3267,10 +3531,10 @@
       <c r="G2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="I2" s="45">
+      <c r="I2" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -3296,10 +3560,10 @@
       <c r="G3" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -3325,10 +3589,10 @@
       <c r="G4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="35">
         <v>45964</v>
       </c>
     </row>
@@ -3354,10 +3618,10 @@
       <c r="G5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -3383,10 +3647,10 @@
       <c r="G6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -3412,10 +3676,10 @@
       <c r="G7" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -3441,10 +3705,10 @@
       <c r="G8" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="59" t="s">
+      <c r="H8" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -3470,10 +3734,10 @@
       <c r="G9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="H9" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -3499,10 +3763,10 @@
       <c r="G10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -3528,10 +3792,10 @@
       <c r="G11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -3557,10 +3821,10 @@
       <c r="G12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -3586,10 +3850,10 @@
       <c r="G13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -3615,10 +3879,10 @@
       <c r="G14" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -3644,10 +3908,10 @@
       <c r="G15" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -3673,10 +3937,10 @@
       <c r="G16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -3702,10 +3966,10 @@
       <c r="G17" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="58" t="s">
+      <c r="H17" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -3731,10 +3995,10 @@
       <c r="G18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="35">
         <v>45964</v>
       </c>
     </row>
@@ -3760,10 +4024,10 @@
       <c r="G19" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H19" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="35">
         <v>45964</v>
       </c>
     </row>
@@ -3792,7 +4056,7 @@
       <c r="H20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I20" s="62">
+      <c r="I20" s="52">
         <v>45966</v>
       </c>
     </row>
@@ -3821,7 +4085,7 @@
       <c r="H21" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="62">
+      <c r="I21" s="52">
         <v>45972</v>
       </c>
     </row>
@@ -3850,7 +4114,7 @@
       <c r="H22" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I22" s="62">
+      <c r="I22" s="52">
         <v>45971</v>
       </c>
     </row>
@@ -3879,7 +4143,7 @@
       <c r="H23" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="62">
+      <c r="I23" s="52">
         <v>45971</v>
       </c>
     </row>
@@ -3908,7 +4172,7 @@
       <c r="H24" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="63">
+      <c r="I24" s="53">
         <v>45964</v>
       </c>
     </row>
@@ -3937,7 +4201,7 @@
       <c r="H25" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="52">
         <v>45986</v>
       </c>
     </row>
@@ -3966,7 +4230,7 @@
       <c r="H26" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="62">
+      <c r="I26" s="52">
         <v>45967</v>
       </c>
     </row>
@@ -3992,10 +4256,10 @@
       <c r="G27" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H27" s="60" t="s">
+      <c r="H27" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -4021,10 +4285,10 @@
       <c r="G28" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="58" t="s">
+      <c r="H28" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="45">
+      <c r="I28" s="35">
         <v>45962</v>
       </c>
     </row>
@@ -4050,10 +4314,10 @@
       <c r="G29" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H29" s="58" t="s">
+      <c r="H29" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="45">
+      <c r="I29" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -4079,10 +4343,10 @@
       <c r="G30" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="58" t="s">
+      <c r="H30" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="45">
+      <c r="I30" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -4108,10 +4372,10 @@
       <c r="G31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="58" t="s">
+      <c r="H31" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="45">
+      <c r="I31" s="35">
         <v>45965</v>
       </c>
     </row>
@@ -4137,10 +4401,10 @@
       <c r="G32" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="58" t="s">
+      <c r="H32" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="I32" s="45">
+      <c r="I32" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -4166,10 +4430,10 @@
       <c r="G33" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="58" t="s">
+      <c r="H33" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="I33" s="45">
+      <c r="I33" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -4195,10 +4459,10 @@
       <c r="G34" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="66" t="s">
+      <c r="H34" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -4210,8 +4474,8 @@
       <c r="E35" s="18"/>
       <c r="F35" s="13"/>
       <c r="G35" s="26"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="65"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="55"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -4221,7 +4485,7 @@
       <c r="E36" s="18"/>
       <c r="F36" s="13"/>
       <c r="G36" s="26"/>
-      <c r="H36" s="64"/>
+      <c r="H36" s="54"/>
       <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
@@ -4231,8 +4495,8 @@
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
       <c r="F37" s="15"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="64"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="54"/>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9">
@@ -4242,8 +4506,8 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="64"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="54"/>
       <c r="I38"/>
     </row>
     <row r="39" spans="1:9">
@@ -4407,7 +4671,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F34">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
@@ -4469,7 +4733,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="61">
+      <c r="B2" s="51">
         <v>45972</v>
       </c>
       <c r="C2" s="28">
@@ -4490,25 +4754,25 @@
       <c r="H2" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="45"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="51">
         <v>45972</v>
       </c>
       <c r="C3" s="28">
         <v>45973</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="59">
         <v>3450141915</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="60" t="s">
         <v>141</v>
       </c>
       <c r="G3" s="26" t="s">
@@ -4517,13 +4781,13 @@
       <c r="H3" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="45"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="51">
         <v>45964</v>
       </c>
       <c r="C4" s="28">
@@ -4544,13 +4808,13 @@
       <c r="H4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="I4" s="45"/>
+      <c r="I4" s="35"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="51">
         <v>45960</v>
       </c>
       <c r="C5" s="28">
@@ -4571,7 +4835,7 @@
       <c r="H5" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -4579,7 +4843,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="51">
         <v>45967</v>
       </c>
       <c r="C6" s="28">
@@ -4600,7 +4864,7 @@
       <c r="H6" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -4608,7 +4872,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="51">
         <v>45996</v>
       </c>
       <c r="C7" s="28">
@@ -4629,7 +4893,7 @@
       <c r="H7" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -4637,7 +4901,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="51">
         <v>45968</v>
       </c>
       <c r="C8" s="28">
@@ -4658,7 +4922,7 @@
       <c r="H8" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4666,7 +4930,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="61">
+      <c r="B9" s="51">
         <v>45967</v>
       </c>
       <c r="C9" s="28">
@@ -4687,7 +4951,7 @@
       <c r="H9" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -4695,7 +4959,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="61">
+      <c r="B10" s="51">
         <v>45968</v>
       </c>
       <c r="C10" s="28">
@@ -4710,13 +4974,13 @@
       <c r="F10" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="57" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4724,7 +4988,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="61">
+      <c r="B11" s="51">
         <v>45968</v>
       </c>
       <c r="C11" s="28">
@@ -4745,7 +5009,7 @@
       <c r="H11" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4753,7 +5017,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="51">
         <v>45968</v>
       </c>
       <c r="C12" s="28">
@@ -4768,13 +5032,13 @@
       <c r="F12" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="57" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4782,7 +5046,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="51">
         <v>45968</v>
       </c>
       <c r="C13" s="28">
@@ -4803,7 +5067,7 @@
       <c r="H13" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4811,7 +5075,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="51">
         <v>45968</v>
       </c>
       <c r="C14" s="28">
@@ -4832,7 +5096,7 @@
       <c r="H14" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -4840,7 +5104,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="51">
         <v>45971</v>
       </c>
       <c r="C15" s="28">
@@ -4861,7 +5125,7 @@
       <c r="H15" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -4869,7 +5133,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="61">
+      <c r="B16" s="51">
         <v>45972</v>
       </c>
       <c r="C16" s="28">
@@ -4890,7 +5154,7 @@
       <c r="H16" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -4898,7 +5162,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="61">
+      <c r="B17" s="51">
         <v>45960</v>
       </c>
       <c r="C17" s="28">
@@ -4919,7 +5183,7 @@
       <c r="H17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -4927,7 +5191,7 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="61">
+      <c r="B18" s="51">
         <v>45960</v>
       </c>
       <c r="C18" s="28">
@@ -4942,13 +5206,13 @@
       <c r="F18" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="67" t="s">
+      <c r="G18" s="57" t="s">
         <v>86</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -4977,7 +5241,7 @@
       <c r="H19" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -5006,7 +5270,7 @@
       <c r="H20" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -5035,7 +5299,7 @@
       <c r="H21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="35">
         <v>45972</v>
       </c>
     </row>
@@ -5058,13 +5322,13 @@
       <c r="F22" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="G22" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="73" t="s">
+      <c r="H22" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="46">
         <v>45964</v>
       </c>
     </row>
@@ -5093,7 +5357,7 @@
       <c r="H23" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="35">
         <v>45964</v>
       </c>
     </row>
@@ -5122,7 +5386,7 @@
       <c r="H24" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="35">
         <v>45961</v>
       </c>
     </row>
@@ -5151,7 +5415,7 @@
       <c r="H25" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -5180,7 +5444,7 @@
       <c r="H26" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="35">
         <v>45966</v>
       </c>
     </row>
@@ -5188,9 +5452,9 @@
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="28"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="34"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="32"/>
       <c r="G27" s="24"/>
       <c r="H27" s="15"/>
     </row>
@@ -5423,10 +5687,10 @@
       <c r="G2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="45"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -5438,22 +5702,22 @@
       <c r="C3" s="7">
         <v>45974</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="58" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="18">
         <v>3450143994</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="60" t="s">
         <v>183</v>
       </c>
       <c r="G3" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="45"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -5477,10 +5741,10 @@
       <c r="G4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -5506,10 +5770,10 @@
       <c r="G5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -5535,10 +5799,10 @@
       <c r="G6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -5564,10 +5828,10 @@
       <c r="G7" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -5593,10 +5857,10 @@
       <c r="G8" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="35">
         <v>45974</v>
       </c>
     </row>
@@ -5622,10 +5886,10 @@
       <c r="G9" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="35">
         <v>45974</v>
       </c>
     </row>
@@ -5651,10 +5915,10 @@
       <c r="G10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -5680,10 +5944,10 @@
       <c r="G11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="35">
         <v>45975</v>
       </c>
     </row>
@@ -5709,10 +5973,10 @@
       <c r="G12" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="35">
         <v>45971</v>
       </c>
     </row>
@@ -5738,10 +6002,10 @@
       <c r="G13" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -5767,10 +6031,10 @@
       <c r="G14" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="74" t="s">
+      <c r="H14" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="35">
         <v>45967</v>
       </c>
     </row>
@@ -5796,10 +6060,10 @@
       <c r="G15" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -5825,10 +6089,10 @@
       <c r="G16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -5854,10 +6118,10 @@
       <c r="G17" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="58" t="s">
+      <c r="H17" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="35">
         <v>45968</v>
       </c>
     </row>
@@ -5883,10 +6147,10 @@
       <c r="G18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -5912,10 +6176,10 @@
       <c r="G19" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H19" s="58" t="s">
+      <c r="H19" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="35">
         <v>45973</v>
       </c>
     </row>
@@ -6289,12 +6553,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="4" max="4" width="19" style="17" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" customWidth="1"/>
@@ -6335,245 +6599,622 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D2" s="66">
+        <v>135203182</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450130740</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="I2" s="35">
+        <v>45967</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="36"/>
+      <c r="B3" s="7">
+        <v>45975</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D3" s="66">
+        <v>135214973</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450132026</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="I3" s="65">
+        <v>45971</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45992</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D4" s="66">
+        <v>135231974</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450133423</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="35">
+        <v>45974</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D5" s="66">
+        <v>135237661</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450133973</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="35">
+        <v>45965</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D6" s="66">
+        <v>135285115</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450133775</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="I6" s="35">
+        <v>45974</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45968</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D7" s="66">
+        <v>135309267</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450140133</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="35">
+        <v>45968</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D8" s="66">
+        <v>135256693</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450135722</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="35">
+        <v>45966</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D9" s="66">
+        <v>135341208</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450142212</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D10" s="66">
+        <v>135349648</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450143158</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>220</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I10" s="35">
+        <v>45974</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D11" s="66">
+        <v>135349913</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450143169</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="I11" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D12" s="66">
+        <v>135353474</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450143587</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I12" s="35">
+        <v>45974</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D13" s="66">
+        <v>135197785</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450129947</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="35">
+        <v>45961</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>45981</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D14" s="66">
+        <v>135215229</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450132060</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="35">
+        <v>45971</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D15" s="66">
+        <v>135216652</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450132191</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>228</v>
+      </c>
+      <c r="I15" s="35">
+        <v>45971</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45966</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D16" s="66">
+        <v>135250749</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450135062</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" s="35">
+        <v>45974</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45967</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D17" s="66">
+        <v>135273340</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450136910</v>
+      </c>
+      <c r="F17" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="35">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D18" s="66">
+        <v>135210735</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450131223</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>230</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="74" t="s">
+        <v>231</v>
+      </c>
+      <c r="I18" s="35">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45963</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D19" s="66">
+        <v>135206428</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450130893</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="35">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45972</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D20" s="66">
+        <v>135322892</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450140991</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>233</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>234</v>
+      </c>
+      <c r="I20" s="35">
+        <v>45975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D21" s="66">
+        <v>135318527</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450140529</v>
+      </c>
+      <c r="F21" s="64" t="s">
+        <v>235</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="35">
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45975</v>
+      </c>
+      <c r="D22" s="66">
+        <v>135223146</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450132939</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I22" s="35">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="8"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="8"/>
       <c r="C24" s="7"/>
@@ -6583,7 +7224,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
@@ -6593,7 +7234,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="8"/>
       <c r="C26" s="7"/>
@@ -6603,7 +7244,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="7"/>
@@ -6613,7 +7254,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="8"/>
       <c r="C28" s="7"/>
@@ -6623,7 +7264,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="8"/>
       <c r="C29" s="7"/>
@@ -6633,7 +7274,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="8"/>
       <c r="C30" s="7"/>
@@ -6643,7 +7284,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="8"/>
       <c r="C31" s="7"/>
@@ -6653,7 +7294,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -6853,27 +7494,17 @@
       <c r="G51" s="6"/>
       <c r="H51" s="9"/>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G37" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6883,7 +7514,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -6919,7 +7550,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="34" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6930,641 +7561,799 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D2" s="66">
+        <v>135212079</v>
+      </c>
+      <c r="E2" s="72">
+        <v>3450131509</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D3" s="66">
+        <v>135214309</v>
+      </c>
+      <c r="E3" s="72">
+        <v>3450131905</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D4" s="66">
+        <v>135219311</v>
+      </c>
+      <c r="E4" s="72">
+        <v>3450132466</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D5" s="66">
+        <v>135221053</v>
+      </c>
+      <c r="E5" s="72">
+        <v>3450132653</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D6" s="66">
+        <v>135229207</v>
+      </c>
+      <c r="E6" s="72">
+        <v>3450133137</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="I6" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45994</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D7" s="66">
+        <v>135222154</v>
+      </c>
+      <c r="E7" s="72">
+        <v>3450132796</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="I7" s="35">
+        <v>45971</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D8" s="66">
+        <v>135222203</v>
+      </c>
+      <c r="E8" s="72">
+        <v>3450132818</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D9" s="66">
+        <v>135221690</v>
+      </c>
+      <c r="E9" s="72">
+        <v>3450132675</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>247</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45995</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D10" s="66">
+        <v>135236513</v>
+      </c>
+      <c r="E10" s="72">
+        <v>3450133841</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="I10" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D11" s="66">
+        <v>135207629</v>
+      </c>
+      <c r="E11" s="72">
+        <v>3450130937</v>
+      </c>
+      <c r="F11" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="G11" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D12" s="66">
+        <v>135208277</v>
+      </c>
+      <c r="E12" s="72">
+        <v>3450130728</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="35">
+        <v>45961</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="27"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="27"/>
+      <c r="B13" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D13" s="66">
+        <v>135208380</v>
+      </c>
+      <c r="E13" s="72">
+        <v>3450130948</v>
+      </c>
+      <c r="F13" s="64" t="s">
+        <v>252</v>
+      </c>
+      <c r="G13" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="35">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1">
+      <c r="A14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D14" s="66">
+        <v>135208539</v>
+      </c>
+      <c r="E14" s="72">
+        <v>3450130959</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D15" s="66">
+        <v>135210020</v>
+      </c>
+      <c r="E15" s="72">
+        <v>3450131157</v>
+      </c>
+      <c r="F15" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="G15" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="27"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="27"/>
+      <c r="B16" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D16" s="66">
+        <v>135211010</v>
+      </c>
+      <c r="E16" s="67">
+        <v>3450130365</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>255</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="35">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D17" s="66">
+        <v>135211849</v>
+      </c>
+      <c r="E17" s="73">
+        <v>3450131421</v>
+      </c>
+      <c r="F17" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="27"/>
+      <c r="B18" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D18" s="66">
+        <v>135212084</v>
+      </c>
+      <c r="E18" s="73">
+        <v>3450130101</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="G18" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="35">
+        <v>45961</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D19" s="66">
+        <v>135213849</v>
+      </c>
+      <c r="E19" s="73">
+        <v>3450131840</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45978</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D20" s="66">
+        <v>135218690</v>
+      </c>
+      <c r="E20" s="73">
+        <v>3450132367</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="G20" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>260</v>
+      </c>
+      <c r="I20" s="35">
+        <v>45971</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D21" s="66">
+        <v>135219384</v>
+      </c>
+      <c r="E21" s="73">
+        <v>3450132488</v>
+      </c>
+      <c r="F21" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="G21" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="35">
+        <v>45964</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D22" s="66">
+        <v>135222769</v>
+      </c>
+      <c r="E22" s="73">
+        <v>3450132895</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="I22" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D23" s="66">
+        <v>135230689</v>
+      </c>
+      <c r="E23" s="73">
+        <v>3450133247</v>
+      </c>
+      <c r="F23" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="35">
+        <v>45965</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D24" s="66">
+        <v>135234887</v>
+      </c>
+      <c r="E24" s="73">
+        <v>3450133742</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="35">
+        <v>45965</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D25" s="66">
+        <v>135236142</v>
+      </c>
+      <c r="E25" s="73">
+        <v>3450133808</v>
+      </c>
+      <c r="F25" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="I25" s="35">
+        <v>45972</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D26" s="66">
+        <v>135240947</v>
+      </c>
+      <c r="E26" s="73">
+        <v>3450134380</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="35">
+        <v>45965</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45977</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D27" s="66">
+        <v>135220277</v>
+      </c>
+      <c r="E27" s="73">
+        <v>3450132565</v>
+      </c>
+      <c r="F27" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I27" s="35">
+        <v>45971</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="27"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="27"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="27"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45965</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45976</v>
+      </c>
+      <c r="D28" s="66">
+        <v>135234370</v>
+      </c>
+      <c r="E28" s="73">
+        <v>3450133710</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>271</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="35">
+        <v>45965</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:F28">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A28" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G28" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7620,22 +8409,22 @@
     <row r="2" spans="1:9">
       <c r="A2" s="6"/>
       <c r="B2" s="28"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="18"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="45"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="48"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="49"/>
+      <c r="G3" s="39"/>
       <c r="H3" s="15"/>
       <c r="I3" s="11"/>
     </row>
@@ -7656,8 +8445,8 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="52"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="42"/>
       <c r="H5" s="13"/>
       <c r="I5" s="11"/>
     </row>
@@ -7668,7 +8457,7 @@
       <c r="D6" s="8"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="52"/>
+      <c r="G6" s="42"/>
       <c r="H6" s="12"/>
       <c r="I6" s="11"/>
     </row>
@@ -7679,7 +8468,7 @@
       <c r="D7" s="8"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="52"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="12"/>
       <c r="I7" s="11"/>
     </row>
@@ -8202,46 +8991,53 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517947</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517947</Url>
-      <Description>QAFFA7D2F2TC-2102087286-517947</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8623,53 +9419,46 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517947</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517947</Url>
+      <Description>QAFFA7D2F2TC-2102087286-517947</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8677,7 +9466,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8685,5 +9474,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>